--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_64982_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_64982_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0a6980f7984a43e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb38ac830c5464db0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4653</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4426</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4171</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4141</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4363</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4264</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_64982_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_64982_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb38ac830c5464db0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ref9c9403fd3242ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6764</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6875</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3485</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3276</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3652</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3674</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3728</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3549</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3561</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3322</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2916</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3128</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2952</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3042</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3031</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2835</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2924</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2792</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3317</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3385</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3518</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3693</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3912</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4653</x:v>
+        <x:v>      0.3807</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4426</x:v>
+        <x:v>      0.3657</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4177</x:v>
+        <x:v>      0.3439</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4171</x:v>
+        <x:v>      0.3451</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4141</x:v>
+        <x:v>      0.3399</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4363</x:v>
+        <x:v>      0.3632</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4214</x:v>
+        <x:v>      0.3473</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4264</x:v>
+        <x:v>      0.3532</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4226</x:v>
+        <x:v>      0.3462</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4189</x:v>
+        <x:v>      0.3468</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4152</x:v>
+        <x:v>      0.3426</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4115</x:v>
+        <x:v>      0.3420</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3999</x:v>
+        <x:v>      0.3282</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3790</x:v>
+        <x:v>      0.3421</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4831</x:v>
+        <x:v>      0.4412</x:v>
       </x:c>
     </x:row>
     <x:row>
